--- a/measurements/31/Filled_2D_sections/coronal/week31_coronal_Batch_Allmarks.xlsx
+++ b/measurements/31/Filled_2D_sections/coronal/week31_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,122 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,34 +616,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.098155859607377</v>
+        <v>1943.310657596372</v>
       </c>
       <c r="D2" t="n">
-        <v>14.6295919156656</v>
+        <v>285.6253659725189</v>
       </c>
       <c r="E2" t="n">
-        <v>10.83942197299585</v>
+        <v>211.6268099489666</v>
       </c>
       <c r="F2" t="n">
         <v>1.349665319065183</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2993357227851718</v>
+        <v>0.2993357227851719</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.060267857142857</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5.422247023809524</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.779327876984127</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.313616071428571</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.422247023809524</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.732607886904761</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.060267857142857</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.4609375</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.80268787202381</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>5.941195716835217</v>
+      <c r="AK2" s="2" t="n">
+        <v>2264.659863945578</v>
       </c>
     </row>
     <row r="3">
@@ -544,17 +693,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.442296252230816</v>
+        <v>2074.489795918367</v>
       </c>
       <c r="D3" t="n">
-        <v>15.94277778195172</v>
+        <v>311.2637566952478</v>
       </c>
       <c r="E3" t="n">
-        <v>11.03454396492097</v>
+        <v>215.436334553219</v>
       </c>
       <c r="F3" t="n">
         <v>1.444806222407932</v>
@@ -563,15 +712,54 @@
         <v>0.2690692433922429</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.27046130952381</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6.793154761904762</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.634827628968254</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.508184523809524</v>
+      </c>
+      <c r="X3" t="n">
+        <v>6.793154761904762</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.221044146825396</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.27046130952381</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.563244047619047</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.048611111111111</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>16.17366047356187</v>
+      <c r="AK3" s="2" t="n">
+        <v>315.7714663885889</v>
       </c>
     </row>
     <row r="4">
@@ -582,34 +770,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.605889351576443</v>
+        <v>2136.848072562358</v>
       </c>
       <c r="D4" t="n">
-        <v>16.11422748100467</v>
+        <v>314.6111079624721</v>
       </c>
       <c r="E4" t="n">
-        <v>11.16904928626084</v>
+        <v>218.0623908269973</v>
       </c>
       <c r="F4" t="n">
         <v>1.442757307985644</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2712910116720424</v>
+        <v>0.2712910116720423</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.941964285714286</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.396949404761904</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.763640873015873</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.619791666666667</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6.396949404761904</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.823288690476191</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.941964285714286</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.725074404761905</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.280133928571428</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>11.43031207235848</v>
+      <c r="AK4" s="2" t="n">
+        <v>223.1632356984274</v>
       </c>
     </row>
     <row r="5">
@@ -620,17 +847,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.656454491374182</v>
+        <v>2156.122448979592</v>
       </c>
       <c r="D5" t="n">
-        <v>16.61386847786787</v>
+        <v>324.3660036155156</v>
       </c>
       <c r="E5" t="n">
-        <v>11.78890812978512</v>
+        <v>230.1643968196142</v>
       </c>
       <c r="F5" t="n">
         <v>1.409279663134562</v>
@@ -639,14 +866,53 @@
         <v>0.2575209852375183</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>13</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.063988095238095</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.19047619047619</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.822973901098901</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.49516369047619</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6.19047619047619</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.712301587301587</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.063988095238095</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.087797619047619</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.821986607142857</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AK5" s="2" t="n">
         <v>1.415407108191172</v>
       </c>
     </row>
@@ -658,17 +924,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.632659131469364</v>
+        <v>2147.052154195011</v>
       </c>
       <c r="D6" t="n">
-        <v>16.74000439411256</v>
+        <v>326.8286572183881</v>
       </c>
       <c r="E6" t="n">
-        <v>11.91749540189417</v>
+        <v>232.6749102274577</v>
       </c>
       <c r="F6" t="n">
         <v>1.404657927659187</v>
@@ -677,24 +943,51 @@
         <v>0.2525877002514463</v>
       </c>
       <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.727678571428571</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23.92857142857143</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9.439306972789115</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.9779916158536586</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.225609756097561</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.10180068597561</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>23.92857142857143</v>
+      </c>
+      <c r="N6" t="n">
+        <v>19.09412202380952</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.727678571428571</v>
+      </c>
+      <c r="X6" t="n">
+        <v>6.73735119047619</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.610491071428571</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0.2877707154111741</v>
+      <c r="AK6" s="2" t="n">
+        <v>0.2877707154111742</v>
       </c>
     </row>
     <row r="7">
@@ -705,17 +998,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.663295657346818</v>
+        <v>2158.730158730159</v>
       </c>
       <c r="D7" t="n">
-        <v>16.22954265373509</v>
+        <v>316.8624994300661</v>
       </c>
       <c r="E7" t="n">
-        <v>11.86973030101962</v>
+        <v>231.7423534960974</v>
       </c>
       <c r="F7" t="n">
         <v>1.367305089681857</v>
@@ -724,24 +1017,60 @@
         <v>0.2701882980746321</v>
       </c>
       <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.060267857142857</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.96763392857143</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.673456101190474</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.9256859756097562</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.9715129573170732</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.9485994664634148</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>18.96763392857143</v>
+      </c>
+      <c r="N7" t="n">
+        <v>18.07291666666666</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7.620907738095237</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5.580357142857142</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.45126488095238</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.818080357142857</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.816220238095238</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.060267857142857</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>1.95</v>
+      <c r="AK7" s="2" t="n">
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -752,43 +1081,79 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.802498512790006</v>
+        <v>2211.791383219955</v>
       </c>
       <c r="D8" t="n">
-        <v>15.84766815348369</v>
+        <v>309.4068544251578</v>
       </c>
       <c r="E8" t="n">
-        <v>11.89830523293193</v>
+        <v>232.300245023909</v>
       </c>
       <c r="F8" t="n">
         <v>1.331926509131804</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2903315045109047</v>
+        <v>0.2903315045109048</v>
       </c>
       <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.09523809523809</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.5537109375</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.9255907012195123</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.926829268292683</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.9262099847560976</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>18.09523809523809</v>
+      </c>
+      <c r="N8" t="n">
+        <v>18.07105654761905</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>7.659970238095237</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7.559523809523809</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.265625</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.77827380952381</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6817716272865854</v>
+      <c r="AK8" s="2" t="n">
+        <v>1.515904017857143</v>
       </c>
     </row>
     <row r="9">
@@ -799,17 +1164,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.99970255800119</v>
+        <v>2286.961451247165</v>
       </c>
       <c r="D9" t="n">
-        <v>15.00901508040545</v>
+        <v>293.0331515698206</v>
       </c>
       <c r="E9" t="n">
-        <v>11.88055102999617</v>
+        <v>231.9536153475443</v>
       </c>
       <c r="F9" t="n">
         <v>1.263326510909341</v>
@@ -818,24 +1183,57 @@
         <v>0.334684189213917</v>
       </c>
       <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.191220238095238</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18.39471726190476</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.513552295918368</v>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.9106326219512195</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.9421684451219513</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.9264005335365855</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>18.39471726190476</v>
+      </c>
+      <c r="N9" t="n">
+        <v>17.77901785714286</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5.504092261904762</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.978794642857143</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.395833333333333</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.351190476190476</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.191220238095238</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.9587402343750001</v>
+      <c r="AK9" s="2" t="n">
+        <v>16.21475074404762</v>
       </c>
     </row>
     <row r="10">
@@ -846,17 +1244,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.342058298631767</v>
+        <v>2417.460317460317</v>
       </c>
       <c r="D10" t="n">
-        <v>16.09647329551418</v>
+        <v>314.2644786267053</v>
       </c>
       <c r="E10" t="n">
-        <v>11.13599225079141</v>
+        <v>217.4169915630704</v>
       </c>
       <c r="F10" t="n">
         <v>1.445445806086138</v>
@@ -865,24 +1263,60 @@
         <v>0.3075945434726268</v>
       </c>
       <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.828497023809524</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.80059523809524</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.081008184523809</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.7066501524390244</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.116615853658537</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.9116330030487805</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>21.80059523809524</v>
+      </c>
+      <c r="N10" t="n">
+        <v>13.79650297619048</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5.669642857142857</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.322916666666666</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3.934151785714286</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.920386904761905</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.375372023809524</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.828497023809524</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.8018382002667683</v>
+      <c r="AK10" s="2" t="n">
+        <v>6.761464701231721</v>
       </c>
     </row>
     <row r="11">
@@ -893,35 +1327,79 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.279595478881618</v>
+        <v>2393.650793650793</v>
       </c>
       <c r="D11" t="n">
-        <v>17.16330534655873</v>
+        <v>335.0931043851943</v>
       </c>
       <c r="E11" t="n">
-        <v>11.231101850184</v>
+        <v>219.2738932654971</v>
       </c>
       <c r="F11" t="n">
         <v>1.528194256939941</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2678796200326617</v>
+        <v>0.2678796200326616</v>
       </c>
       <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.506696428571428</v>
+      </c>
+      <c r="J11" t="n">
+        <v>21.15885416666666</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.050362723214285</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.631859756097561</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.08374618902439</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.8578029725609756</v>
+      <c r="M11" t="n">
+        <v>21.15885416666666</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12.33630952380952</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8.517485119047619</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7.855282738095237</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.494419642857142</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.840401785714286</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.693452380952381</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.506696428571428</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="12">
@@ -932,17 +1410,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.142772159428912</v>
+        <v>2341.496598639455</v>
       </c>
       <c r="D12" t="n">
-        <v>18.93817243634201</v>
+        <v>369.7452713762011</v>
       </c>
       <c r="E12" t="n">
-        <v>11.4154030549817</v>
+        <v>222.872154882976</v>
       </c>
       <c r="F12" t="n">
         <v>1.659001644105537</v>
@@ -951,16 +1429,57 @@
         <v>0.2152276868384635</v>
       </c>
       <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.379092261904762</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20.3515625</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9.6435546875</v>
+      </c>
+      <c r="L12" t="n">
         <v>4</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.591844512195122</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.042397103658537</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.7635289634146342</v>
+      <c r="P12" t="n">
+        <v>11.55505952380952</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>20.3515625</v>
+      </c>
+      <c r="R12" t="n">
+        <v>14.90699404761905</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7.32328869047619</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.401041666666666</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.41703869047619</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.379092261904762</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>18.54195283882784</v>
       </c>
     </row>
     <row r="13">
@@ -971,17 +1490,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.276026174895896</v>
+        <v>2392.290249433107</v>
       </c>
       <c r="D13" t="n">
-        <v>17.53681041263953</v>
+        <v>342.3853461515336</v>
       </c>
       <c r="E13" t="n">
-        <v>11.62827916843135</v>
+        <v>227.0283075741359</v>
       </c>
       <c r="F13" t="n">
         <v>1.508117422932944</v>
@@ -990,16 +1509,60 @@
         <v>0.2564445042757309</v>
       </c>
       <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.294642857142857</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19.83444940476191</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.456798735119047</v>
+      </c>
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.6316692073170732</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.015910823170732</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.776391006097561</v>
+      <c r="M13" t="n">
+        <v>19.83444940476191</v>
+      </c>
+      <c r="N13" t="n">
+        <v>13.30729166666667</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12.33258928571428</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8.798363095238095</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.957217261904762</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.546130952380953</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.583705357142857</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.294642857142857</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>14.30338541666667</v>
       </c>
     </row>
     <row r="14">
@@ -1010,35 +1573,76 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.383402736466389</v>
+        <v>2433.219954648526</v>
       </c>
       <c r="D14" t="n">
-        <v>17.38455089127145</v>
+        <v>339.4126602581569</v>
       </c>
       <c r="E14" t="n">
-        <v>11.6366486055095</v>
+        <v>227.1917108694712</v>
       </c>
       <c r="F14" t="n">
-        <v>1.49394825611908</v>
+        <v>1.493948256119081</v>
       </c>
       <c r="G14" t="n">
         <v>0.2654209248246228</v>
       </c>
       <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.016369047619047</v>
+      </c>
+      <c r="J14" t="n">
+        <v>19.55915178571428</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.173363095238095</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.5569740853658537</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.001810213414634</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.7291031504065041</v>
+      <c r="M14" t="n">
+        <v>19.55915178571428</v>
+      </c>
+      <c r="N14" t="n">
+        <v>12.27120535714286</v>
+      </c>
+      <c r="O14" t="n">
+        <v>10.87425595238095</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4.157366071428571</v>
+      </c>
+      <c r="X14" t="n">
+        <v>7.217261904761904</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.166480654761905</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.016369047619047</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>10.96261160714286</v>
       </c>
     </row>
     <row r="15">
@@ -1049,17 +1653,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.492861392028555</v>
+        <v>2474.943310657596</v>
       </c>
       <c r="D15" t="n">
-        <v>16.19504962316374</v>
+        <v>316.189064071292</v>
       </c>
       <c r="E15" t="n">
-        <v>11.5676625850724</v>
+        <v>225.8448409466516</v>
       </c>
       <c r="F15" t="n">
         <v>1.400027836571131</v>
@@ -1068,16 +1672,57 @@
         <v>0.3110866897494513</v>
       </c>
       <c r="H15" t="n">
+        <v>9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.434151785714286</v>
+      </c>
+      <c r="J15" t="n">
+        <v>19.29873511904762</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6.793568121693122</v>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.518578506097561</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.9884717987804879</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.7535251524390244</v>
+      <c r="M15" t="n">
+        <v>19.29873511904762</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10.12462797619048</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.733258928571428</v>
+      </c>
+      <c r="X15" t="n">
+        <v>8.655133928571429</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.755208333333333</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.508556547619047</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.434151785714286</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>10.32862103174603</v>
       </c>
     </row>
     <row r="16">
@@ -1088,35 +1733,76 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.506841165972635</v>
+        <v>2480.272108843537</v>
       </c>
       <c r="D16" t="n">
-        <v>14.94594710919915</v>
+        <v>291.8018245129358</v>
       </c>
       <c r="E16" t="n">
-        <v>11.43805992021793</v>
+        <v>223.3145032042549</v>
       </c>
       <c r="F16" t="n">
         <v>1.306685505535836</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3660439115187639</v>
+        <v>0.366043911518764</v>
       </c>
       <c r="H16" t="n">
+        <v>9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9933035714285714</v>
+      </c>
+      <c r="J16" t="n">
+        <v>12.45535714285714</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.516286375661375</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.6379573170731707</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.6379573170731707</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.6379573170731707</v>
+      <c r="M16" t="n">
+        <v>12.45535714285714</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.833705357142857</v>
+      </c>
+      <c r="X16" t="n">
+        <v>9.270833333333332</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7.676711309523809</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9933035714285714</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.176339285714286</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.62109375</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>19.48226686507937</v>
       </c>
     </row>
     <row r="17">
@@ -1127,35 +1813,73 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.346519928613921</v>
+        <v>2419.160997732426</v>
       </c>
       <c r="D17" t="n">
-        <v>16.36159663084077</v>
+        <v>319.4406961259388</v>
       </c>
       <c r="E17" t="n">
-        <v>11.49867655009758</v>
+        <v>224.4979707400004</v>
       </c>
       <c r="F17" t="n">
         <v>1.422911285447186</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2979162199641909</v>
+        <v>0.297916219964191</v>
       </c>
       <c r="H17" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.099330357142857</v>
+      </c>
+      <c r="J17" t="n">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.917782738095237</v>
+      </c>
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.505907012195122</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.975609756097561</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.6623951981707317</v>
+      <c r="P17" t="n">
+        <v>9.877232142857142</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="R17" t="n">
+        <v>12.93247767857143</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.099330357142857</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.983630952380952</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.106026785714286</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>13.62552703373016</v>
       </c>
     </row>
     <row r="18">
@@ -1166,17 +1890,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.21772754312909</v>
+        <v>2370.068027210884</v>
       </c>
       <c r="D18" t="n">
-        <v>16.19403423914095</v>
+        <v>316.1692399070376</v>
       </c>
       <c r="E18" t="n">
-        <v>11.59378618147315</v>
+        <v>226.3548730668567</v>
       </c>
       <c r="F18" t="n">
         <v>1.396785656183568</v>
@@ -1185,16 +1909,57 @@
         <v>0.2979418055480595</v>
       </c>
       <c r="H18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.062127976190476</v>
+      </c>
+      <c r="J18" t="n">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.722284226190476</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>9.553571428571429</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="R18" t="n">
+        <v>13.037109375</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.376116071428571</v>
+      </c>
+      <c r="Z18" t="n">
         <v>3</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.5933689024390244</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.975609756097561</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.7272294207317073</v>
+      <c r="AA18" t="n">
+        <v>2.892485119047619</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.299107142857143</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.062127976190476</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="19">
@@ -1205,35 +1970,79 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.019631171921476</v>
+        <v>2294.557823129252</v>
       </c>
       <c r="D19" t="n">
-        <v>15.80379036577737</v>
+        <v>308.5501928556533</v>
       </c>
       <c r="E19" t="n">
-        <v>11.31784208227949</v>
+        <v>220.9673930349804</v>
       </c>
       <c r="F19" t="n">
         <v>1.396360741816816</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3028706754225622</v>
+        <v>0.3028706754225623</v>
       </c>
       <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.062127976190476</v>
+      </c>
+      <c r="J19" t="n">
+        <v>19.30803571428571</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.635556175595238</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>19.30803571428571</v>
+      </c>
+      <c r="N19" t="n">
+        <v>12.1391369047619</v>
+      </c>
+      <c r="O19" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8.117559523809524</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.936755952380953</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.008556547619047</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.6217606707317074</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.9889481707317074</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.8053544207317074</v>
+      <c r="AA19" t="n">
+        <v>1.988467261904762</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.062127976190476</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="n">
+        <v>7.024925595238095</v>
       </c>
     </row>
     <row r="20">
@@ -1244,35 +2053,79 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.751338488994646</v>
+        <v>2192.290249433107</v>
       </c>
       <c r="D20" t="n">
-        <v>14.68327511519921</v>
+        <v>286.6734665348416</v>
       </c>
       <c r="E20" t="n">
-        <v>11.15966447097499</v>
+        <v>217.8791634809403</v>
       </c>
       <c r="F20" t="n">
         <v>1.315745213791035</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3352223143936678</v>
+        <v>0.335222314393668</v>
       </c>
       <c r="H20" t="n">
+        <v>9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9505208333333333</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12.67485119047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.042493386243386</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.6023246951219512</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.6491996951219512</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.6257621951219512</v>
+      <c r="M20" t="n">
+        <v>12.67485119047619</v>
+      </c>
+      <c r="N20" t="n">
+        <v>11.75967261904762</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.735119047619047</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.457868303571428</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.964285714285714</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.201636904761905</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.9505208333333333</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>5.2354083994709</v>
       </c>
     </row>
     <row r="21">
@@ -1283,17 +2136,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.164187983343249</v>
+        <v>1968.480725623583</v>
       </c>
       <c r="D21" t="n">
-        <v>15.04350806736365</v>
+        <v>293.7065860770998</v>
       </c>
       <c r="E21" t="n">
-        <v>10.58511940735142</v>
+        <v>206.6618550959087</v>
       </c>
       <c r="F21" t="n">
         <v>1.421193988318719</v>
@@ -1302,16 +2155,60 @@
         <v>0.2867567570448058</v>
       </c>
       <c r="H21" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.125372023809524</v>
+      </c>
+      <c r="J21" t="n">
+        <v>15.56919642857143</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.015438988095237</v>
+      </c>
+      <c r="L21" t="n">
         <v>3</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.5695503048780488</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.7974466463414634</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.6757177337398375</v>
+      <c r="M21" t="n">
+        <v>15.56919642857143</v>
+      </c>
+      <c r="N21" t="n">
+        <v>12.88876488095238</v>
+      </c>
+      <c r="O21" t="n">
+        <v>11.11979166666667</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7.661830357142857</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.526785714285714</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.202380952380952</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.029389880952381</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.125372023809524</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="n">
+        <v>4.514508928571428</v>
       </c>
     </row>
     <row r="22">
@@ -1321,7 +2218,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>3.791542658730158</v>
       </c>
     </row>
     <row r="23">
@@ -1335,6 +2240,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>7.250537367724868</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1344,6 +2257,120 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>5.461777998236331</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>2.367359203296703</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>1.939596861471862</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>1.371837797619047</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>1.238219246031746</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>2.666170634920635</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>1.946756675760582</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/31/Filled_2D_sections/coronal/week31_coronal_Batch_Allmarks.xlsx
+++ b/measurements/31/Filled_2D_sections/coronal/week31_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2376,4 +2582,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week31_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2264.659863945578</v>
+      </c>
+      <c r="D10" t="n">
+        <v>163.1961084975368</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1943.310657596372</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2480.272108843537</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>315.7714663885889</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20.79387850561801</v>
+      </c>
+      <c r="E11" t="n">
+        <v>285.6253659725189</v>
+      </c>
+      <c r="F11" t="n">
+        <v>369.7452713762011</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.415407108191172</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.08855950696392713</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.263326510909341</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.659001644105537</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2877707154111741</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03426976243518418</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2152276868384635</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.366043911518764</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0090.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0094.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0097.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0101.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0104.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0107.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0111.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0114.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0117.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0121.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0124.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0128.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0131.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0155.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.79105966869954</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7</v>
+      </c>
+      <c r="F40" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.316894273021107</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.02874085917453</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.823819012257983</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>41</v>
+      </c>
+      <c r="C48" t="n">
+        <v>15.12299470092915</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4.032095940434997</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="F48" t="n">
+        <v>23.92857142857143</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>74</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.465306266087516</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.632940244881388</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.376116071428571</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.270833333333332</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>64</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.960972377232143</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5741620798038007</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9505208333333333</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.087797619047619</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>